--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487164_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487164_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5168</v>
+        <v>7.4262</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0445</v>
+        <v>5.7034</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4723</v>
+        <v>1.7228</v>
       </c>
       <c r="G2" t="n">
         <v>4.1724</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9234</v>
+        <v>0.8328</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5619</v>
+        <v>0.2208</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3616</v>
+        <v>0.612</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7308</v>
+        <v>7.4179</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8654</v>
+        <v>7.5257</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1346</v>
+        <v>-0.1078</v>
       </c>
       <c r="G3" t="n">
         <v>6.1785</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6127</v>
+        <v>1.2998</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0423</v>
+        <v>0.7027</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5704</v>
+        <v>0.5972</v>
       </c>
       <c r="V3" t="n">
         <v>3.0277</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8864</v>
+        <v>3.4834</v>
       </c>
       <c r="E4" t="n">
-        <v>2.631</v>
+        <v>1.3886</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2554</v>
+        <v>2.0948</v>
       </c>
       <c r="G4" t="n">
         <v>0.1756</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6096</v>
+        <v>1.2066</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2368</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3727</v>
+        <v>0.2121</v>
       </c>
       <c r="V4" t="n">
         <v>1.7152</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9135</v>
+        <v>1.7132</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0527</v>
+        <v>0.8525</v>
       </c>
       <c r="F5" t="n">
         <v>0.8607</v>
@@ -844,10 +844,10 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1481</v>
+        <v>-0.0522</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2062</v>
+        <v>0.006</v>
       </c>
       <c r="U5" t="n">
         <v>-0.0582</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ MENDIGUCHIA</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4298</v>
+        <v>-0.2549</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.494</v>
+        <v>-2.3464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06419999999999999</v>
+        <v>2.0915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2752</v>
+        <v>-1.6288</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5195</v>
+        <v>-2.3649</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7947</v>
+        <v>0.7361</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0414</v>
+        <v>-1.6094</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0414</v>
+        <v>-2.5048</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.8954</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2338</v>
+        <v>-0.0194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5609</v>
+        <v>0.1399</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7947</v>
+        <v>-0.1592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9981</v>
+        <v>0.9878</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5354</v>
+        <v>0.2281</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4627</v>
+        <v>0.7598</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>P. FERNANDEZ MENDIGUCHIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4344</v>
+        <v>-0.3227</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6062</v>
+        <v>-0.494</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1718</v>
+        <v>0.1713</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6288</v>
+        <v>0.2752</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3649</v>
+        <v>-0.5195</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7361</v>
+        <v>0.7947</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6094</v>
+        <v>0.0414</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5048</v>
+        <v>0.0414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8954</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0194</v>
+        <v>0.2338</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1399</v>
+        <v>-0.5609</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1592</v>
+        <v>0.7947</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8084</v>
+        <v>-0.891</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0317</v>
+        <v>-0.5354</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8401</v>
+        <v>-0.3556</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.7873</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9508</v>
+        <v>1.7505</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5914</v>
+        <v>-2.5379</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6532</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5843</v>
+        <v>0.4376</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6821</v>
+        <v>0.4819</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5717</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6161</v>
+        <v>-1.2086</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2539</v>
+        <v>-0.9535</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3622</v>
+        <v>-0.2551</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2987</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3246</v>
+        <v>-0.9171</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7297</v>
+        <v>-0.6227</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5717</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7977</v>
+        <v>-2.3482</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3886</v>
+        <v>-2.528</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4091</v>
+        <v>0.1798</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5173</v>
@@ -1234,13 +1234,13 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3154</v>
+        <v>0.1342</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8037</v>
+        <v>0.0569</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8263</v>
+        <v>-4.5189</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5748</v>
+        <v>-2.3745</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2515</v>
+        <v>-2.1444</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1636</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2261</v>
+        <v>0.0813</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4442</v>
+        <v>0.6445</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6703</v>
+        <v>-0.5632</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4716</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.3026</v>
+        <v>10.6001</v>
       </c>
       <c r="E12" t="n">
-        <v>8.226900000000002</v>
+        <v>8.524299999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0756</v>
+        <v>2.0757</v>
       </c>
       <c r="G12" t="n">
         <v>3.533499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>11.5805</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8223</v>
+        <v>3.1198</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2078</v>
+        <v>2.5055</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6145000000000002</v>
+        <v>0.6143999999999997</v>
       </c>
       <c r="V12" t="n">
         <v>4.911999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0719</v>
+        <v>1.4842</v>
       </c>
       <c r="E13" t="n">
-        <v>1.342</v>
+        <v>0.5409</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7299</v>
+        <v>0.9434</v>
       </c>
       <c r="G13" t="n">
         <v>0.6637999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5129</v>
+        <v>-0.0747</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7681</v>
+        <v>-0.033</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2552</v>
+        <v>-0.0417</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.5365</v>
       </c>
       <c r="E14" t="n">
         <v>-0.2409</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.7774</v>
       </c>
       <c r="G14" t="n">
         <v>0.4138</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5764</v>
+        <v>0.4158</v>
       </c>
       <c r="T14" t="n">
         <v>0.3252</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2512</v>
+        <v>0.0905</v>
       </c>
       <c r="V14" t="n">
         <v>0.2859</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3764</v>
+        <v>0.0116</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3439</v>
+        <v>-0.5442</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0324</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0.7618</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7522</v>
+        <v>-0.3642</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3385</v>
+        <v>0.1382</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0907</v>
+        <v>-0.5024</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9786</v>
+        <v>-0.6822</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1236</v>
+        <v>-1.2985</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1451</v>
+        <v>0.6162</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.194</v>
+        <v>-3.4191</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6417</v>
+        <v>0.7329</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4477</v>
+        <v>-4.152</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7337</v>
+        <v>-2.7263</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1397</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5941</v>
+        <v>-2.6383</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9277</v>
+        <v>-0.6928</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7813</v>
+        <v>0.8209</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1464</v>
+        <v>-1.5137</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1805</v>
+        <v>-0.3378</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0727</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1077</v>
+        <v>-0.428</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.1977</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.1977</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.261</v>
+        <v>-0.8803</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2295</v>
+        <v>0.0709</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0315</v>
+        <v>-0.9512</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2989</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5255</v>
+        <v>-0.1448</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1785</v>
+        <v>0.122</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V17" t="n">
         <v>0.3704</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4371</v>
+        <v>-1.1521</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5989</v>
+        <v>-1.3239</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1618</v>
+        <v>0.1718</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4191</v>
+        <v>-0.194</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7329</v>
+        <v>-0.6417</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.152</v>
+        <v>0.4477</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.7263</v>
+        <v>0.7337</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.1397</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6383</v>
+        <v>0.5941</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6928</v>
+        <v>-0.9277</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8209</v>
+        <v>-0.7813</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5137</v>
+        <v>-0.1464</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0926</v>
+        <v>0.0069</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2102</v>
+        <v>-0.1276</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8824</v>
+        <v>0.1345</v>
       </c>
       <c r="V18" t="n">
-        <v>5.1977</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>5.1977</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6086</v>
+        <v>-1.4754</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2637</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3449</v>
+        <v>-1.2117</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4218</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8467</v>
+        <v>-0.7135</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6411</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2056</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2702</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6771</v>
+        <v>-1.6449</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9708</v>
+        <v>-0.3151</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6479</v>
+        <v>-1.3298</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3935</v>
+        <v>-0.4323</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0265</v>
+        <v>1.6548</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.633</v>
+        <v>-2.0871</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3743</v>
+        <v>-0.2864</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9198</v>
+        <v>0.9674</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5455</v>
+        <v>-1.2538</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9808</v>
+        <v>-0.1459</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1067</v>
+        <v>0.6874</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0875</v>
+        <v>-0.8333</v>
       </c>
       <c r="P20" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0007</v>
+        <v>0.657</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3107</v>
+        <v>-0.0287</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3113</v>
+        <v>0.6857</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4559</v>
+        <v>-3.0277</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7418</v>
+        <v>-3.0277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7844</v>
+        <v>-1.8436</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6155</v>
+        <v>1.6704</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1688</v>
+        <v>-3.514</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4323</v>
+        <v>0.3935</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6548</v>
+        <v>2.0265</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0871</v>
+        <v>-1.633</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2864</v>
+        <v>1.3743</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9674</v>
+        <v>1.9198</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2538</v>
+        <v>-0.5455</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1459</v>
+        <v>-0.9808</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6874</v>
+        <v>0.1067</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8333</v>
+        <v>-1.0875</v>
       </c>
       <c r="P21" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5175</v>
+        <v>-0.1672</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3291</v>
+        <v>0.0103</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8467</v>
+        <v>-0.1775</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0277</v>
+        <v>-2.4559</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.0277</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9485</v>
+        <v>-3.3212</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9724</v>
+        <v>-0.3716</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.976</v>
+        <v>-2.9496</v>
       </c>
       <c r="G22" t="n">
         <v>0.9997</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.392</v>
+        <v>-0.7648</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0708</v>
+        <v>-0.4699</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3213</v>
+        <v>-0.2948</v>
       </c>
       <c r="V22" t="n">
         <v>-2.784</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.3027</v>
+        <v>-8.967400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0756</v>
+        <v>-2.0757</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.226700000000001</v>
+        <v>-6.8916</v>
       </c>
       <c r="G23" t="n">
         <v>-3.533499999999999</v>
@@ -2236,10 +2236,10 @@
         <v>1.2329</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.300600000000001</v>
+        <v>-8.300599999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.9650999999999994</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5805</v>
@@ -2248,13 +2248,13 @@
         <v>12.5455</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8224</v>
+        <v>-1.4873</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6145</v>
+        <v>-0.6143000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.2079</v>
+        <v>-0.8728</v>
       </c>
       <c r="V23" t="n">
         <v>-4.911799999999999</v>
